--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_br_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_br_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2021 08:30</t>
+          <t>2021-02-04 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>27-02-2021 08:30</t>
+          <t>2021-02-27 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>27-02-2021 08:30</t>
+          <t>2021-02-27 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>27-02-2021 08:30</t>
+          <t>2021-02-27 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>27-02-2021 08:30</t>
+          <t>2021-02-27 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>27-02-2021 08:30</t>
+          <t>2021-02-27 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9363,7 +9363,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="inlineStr"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -11223,7 +11223,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="inlineStr"/>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr"/>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11781,7 +11781,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -12897,7 +12897,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr"/>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr"/>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="inlineStr"/>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="inlineStr"/>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr"/>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr"/>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="inlineStr"/>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr"/>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr"/>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="inlineStr"/>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="inlineStr"/>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="inlineStr"/>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr"/>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="inlineStr"/>
@@ -14385,7 +14385,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="inlineStr"/>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="inlineStr"/>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="inlineStr"/>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="inlineStr"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="inlineStr"/>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr"/>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15408,7 +15408,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15501,7 +15501,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="inlineStr"/>
@@ -15966,7 +15966,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="inlineStr"/>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="inlineStr"/>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="inlineStr"/>
@@ -16245,7 +16245,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="inlineStr"/>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="inlineStr"/>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="inlineStr"/>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="inlineStr"/>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="inlineStr"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr"/>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -16896,7 +16896,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -16989,7 +16989,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -17175,7 +17175,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="inlineStr"/>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17454,7 +17454,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="inlineStr"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="inlineStr"/>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -17826,7 +17826,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr"/>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="inlineStr"/>
@@ -18105,7 +18105,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="inlineStr"/>
@@ -18198,7 +18198,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="inlineStr"/>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
@@ -18570,7 +18570,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
@@ -18663,7 +18663,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="inlineStr"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="inlineStr"/>
@@ -19128,7 +19128,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -19221,7 +19221,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
@@ -19314,7 +19314,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="inlineStr"/>
@@ -19407,7 +19407,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="inlineStr"/>
@@ -19500,7 +19500,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="inlineStr"/>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -19779,7 +19779,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr"/>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -20058,7 +20058,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr"/>
@@ -20430,7 +20430,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -20523,7 +20523,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -20988,7 +20988,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="n">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="n">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="n">
@@ -21291,7 +21291,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>03-10-2021 08:30</t>
+          <t>2021-03-10 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="n">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="n">
@@ -21493,7 +21493,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="n">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="n">
@@ -21695,7 +21695,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>03-10-2021 08:30</t>
+          <t>2021-03-10 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="n">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -21897,7 +21897,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -21998,7 +21998,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="n">
@@ -22099,7 +22099,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="n">
@@ -22200,7 +22200,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="n">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="n">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="n">
@@ -22503,7 +22503,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="n">
@@ -22604,7 +22604,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="n">
@@ -22705,7 +22705,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="n">
@@ -22806,7 +22806,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="n">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="n">
@@ -23008,7 +23008,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="n">
@@ -23109,7 +23109,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="n">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>03-10-2021 08:30</t>
+          <t>2021-03-10 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23311,7 +23311,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -23513,7 +23513,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="n">
@@ -23614,7 +23614,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>02-10-2021 08:30</t>
+          <t>2021-02-10 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="n">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="n">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="n">
@@ -23917,7 +23917,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="n">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="n">
@@ -24119,7 +24119,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="n">
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="n">
@@ -24321,7 +24321,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="n">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="n">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -24725,7 +24725,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>31-10-2021 08:30</t>
+          <t>2021-10-31 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
@@ -24826,7 +24826,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -24927,7 +24927,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -25129,7 +25129,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -25230,7 +25230,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="n">
@@ -25331,7 +25331,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="n">
@@ -25432,7 +25432,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="n">
@@ -25533,7 +25533,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="n">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="n">
@@ -25735,7 +25735,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="n">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="n">
@@ -25937,7 +25937,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="n">
@@ -26038,7 +26038,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="n">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="n">
@@ -26240,7 +26240,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="n">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="n">
@@ -26442,7 +26442,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="n">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="n">
@@ -26644,7 +26644,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="n">
@@ -26745,7 +26745,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="n">
@@ -26846,7 +26846,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="n">
@@ -26947,7 +26947,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="n">
@@ -27048,7 +27048,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="n">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="n">
@@ -27250,7 +27250,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="n">
@@ -27351,7 +27351,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="n">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="n">
@@ -27553,7 +27553,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="n">
@@ -27654,7 +27654,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="n">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="n">
@@ -27856,7 +27856,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="n">
@@ -27957,7 +27957,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="n">
@@ -28058,7 +28058,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="n">
@@ -28159,7 +28159,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="n">
@@ -28260,7 +28260,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="n">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="n">
@@ -28462,7 +28462,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="n">
@@ -28563,7 +28563,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="n">
@@ -28664,7 +28664,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="n">
@@ -28765,7 +28765,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="n">
@@ -28866,7 +28866,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="n">
@@ -28967,7 +28967,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="n">
@@ -29068,7 +29068,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="inlineStr"/>
@@ -29161,7 +29161,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="inlineStr"/>
@@ -29254,7 +29254,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="inlineStr"/>
@@ -29347,7 +29347,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="inlineStr"/>
@@ -29440,7 +29440,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="inlineStr"/>
@@ -29533,7 +29533,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="inlineStr"/>
@@ -29626,7 +29626,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="inlineStr"/>
@@ -29719,7 +29719,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="inlineStr"/>
@@ -29812,7 +29812,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="inlineStr"/>
@@ -29905,7 +29905,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="inlineStr"/>
@@ -29998,7 +29998,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="inlineStr"/>
@@ -30091,7 +30091,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="inlineStr"/>
@@ -30184,7 +30184,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="inlineStr"/>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="inlineStr"/>
@@ -30370,7 +30370,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="inlineStr"/>
@@ -30463,7 +30463,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="inlineStr"/>
@@ -30556,7 +30556,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="inlineStr"/>
@@ -30649,7 +30649,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="inlineStr"/>
@@ -30742,7 +30742,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="inlineStr"/>
@@ -30835,7 +30835,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="inlineStr"/>
@@ -30928,7 +30928,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="inlineStr"/>
@@ -31021,7 +31021,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="inlineStr"/>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="inlineStr"/>
@@ -31207,7 +31207,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="n">
@@ -31302,7 +31302,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="n">
@@ -31397,7 +31397,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="n">
@@ -31492,7 +31492,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>30-06-2021 08:30</t>
+          <t>2021-06-30 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="n">
@@ -31587,7 +31587,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="n">
@@ -31777,7 +31777,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="n">
@@ -31872,7 +31872,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="inlineStr"/>
@@ -31965,7 +31965,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="inlineStr"/>
@@ -32058,7 +32058,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="inlineStr"/>
@@ -32151,7 +32151,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="inlineStr"/>
@@ -32244,7 +32244,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="inlineStr"/>
@@ -32337,7 +32337,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>27-03-2021 08:30</t>
+          <t>2021-03-27 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="inlineStr"/>
@@ -32430,7 +32430,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="inlineStr"/>
@@ -32523,7 +32523,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32616,7 +32616,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="inlineStr"/>
@@ -32709,7 +32709,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="inlineStr"/>
@@ -32802,7 +32802,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="inlineStr"/>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>27-03-2021 08:30</t>
+          <t>2021-03-27 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -32988,7 +32988,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="inlineStr"/>
@@ -33081,7 +33081,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="inlineStr"/>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -33267,7 +33267,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -33360,7 +33360,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -33453,7 +33453,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="inlineStr"/>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -33639,7 +33639,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="inlineStr"/>
@@ -33732,7 +33732,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -33825,7 +33825,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -33918,7 +33918,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="inlineStr"/>
@@ -34011,7 +34011,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="inlineStr"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="inlineStr"/>
@@ -34197,7 +34197,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="n">
@@ -34292,7 +34292,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="n">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="n">
@@ -34482,7 +34482,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="n">
@@ -34577,7 +34577,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="n">
@@ -34672,7 +34672,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -34767,7 +34767,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="n">
@@ -34862,7 +34862,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>02-10-2021 08:30</t>
+          <t>2021-02-10 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="n">
@@ -34957,7 +34957,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>18-11-2021 08:30</t>
+          <t>2021-11-18 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="n">
@@ -35052,7 +35052,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="n">
@@ -35147,7 +35147,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="inlineStr"/>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="inlineStr"/>
@@ -35333,7 +35333,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>27-03-2021 08:30</t>
+          <t>2021-03-27 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="inlineStr"/>
@@ -35426,7 +35426,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="n">
@@ -35527,7 +35527,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="inlineStr"/>
@@ -35620,7 +35620,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="inlineStr"/>
@@ -35713,7 +35713,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="inlineStr"/>
@@ -35806,7 +35806,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="inlineStr"/>
@@ -35899,7 +35899,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="inlineStr"/>
@@ -35992,7 +35992,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="inlineStr"/>
@@ -36085,7 +36085,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="inlineStr"/>
@@ -36178,7 +36178,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="inlineStr"/>
@@ -36271,7 +36271,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
@@ -36364,7 +36364,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="inlineStr"/>
@@ -36457,7 +36457,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="inlineStr"/>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="inlineStr"/>
@@ -36643,7 +36643,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="inlineStr"/>
@@ -36736,7 +36736,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="inlineStr"/>
@@ -36829,7 +36829,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="inlineStr"/>
@@ -36922,7 +36922,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="inlineStr"/>
@@ -37015,7 +37015,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="inlineStr"/>
@@ -37108,7 +37108,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="inlineStr"/>
@@ -37201,7 +37201,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="inlineStr"/>
@@ -37294,7 +37294,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="inlineStr"/>
@@ -37387,7 +37387,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="inlineStr"/>
@@ -37480,7 +37480,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="inlineStr"/>
@@ -37573,7 +37573,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="inlineStr"/>
@@ -37666,7 +37666,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="inlineStr"/>
@@ -37759,7 +37759,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="inlineStr"/>
@@ -37852,7 +37852,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="inlineStr"/>
@@ -37945,7 +37945,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="inlineStr"/>
@@ -38038,7 +38038,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="inlineStr"/>
@@ -38131,7 +38131,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="inlineStr"/>
@@ -38224,7 +38224,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="inlineStr"/>
@@ -38317,7 +38317,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="inlineStr"/>
@@ -38410,7 +38410,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="inlineStr"/>
@@ -38503,7 +38503,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="inlineStr"/>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="inlineStr"/>
@@ -38689,7 +38689,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="inlineStr"/>
@@ -38782,7 +38782,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="inlineStr"/>
@@ -38875,7 +38875,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="inlineStr"/>
@@ -38968,7 +38968,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="inlineStr"/>
@@ -39061,7 +39061,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="inlineStr"/>
@@ -39154,7 +39154,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="inlineStr"/>
@@ -39247,7 +39247,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="inlineStr"/>
@@ -39340,7 +39340,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="inlineStr"/>
@@ -39433,7 +39433,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="inlineStr"/>
@@ -39526,7 +39526,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="inlineStr"/>
@@ -39619,7 +39619,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="inlineStr"/>
@@ -39712,7 +39712,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="inlineStr"/>
@@ -39805,7 +39805,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="inlineStr"/>
@@ -39898,7 +39898,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="inlineStr"/>
@@ -39991,7 +39991,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="inlineStr"/>
@@ -40084,7 +40084,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="inlineStr"/>
@@ -40177,7 +40177,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="inlineStr"/>
@@ -40270,7 +40270,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="inlineStr"/>
@@ -40363,7 +40363,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="inlineStr"/>
@@ -40456,7 +40456,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="inlineStr"/>
@@ -40549,7 +40549,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="inlineStr"/>
@@ -40642,7 +40642,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="inlineStr"/>
@@ -40735,7 +40735,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>31-01-2021 08:30</t>
+          <t>2021-01-31 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="n">
@@ -40830,7 +40830,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>27-02-2021 08:30</t>
+          <t>2021-02-27 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="n">
@@ -40925,7 +40925,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="n">
@@ -41020,7 +41020,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>19-05-2021 08:30</t>
+          <t>2021-05-19 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="n">
@@ -41115,7 +41115,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>12-06-2021 08:30</t>
+          <t>2021-12-06 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="n">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>10-07-2021 08:30</t>
+          <t>2021-10-07 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="n">
@@ -41305,7 +41305,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>07-08-2021 08:30</t>
+          <t>2021-07-08 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="n">
@@ -41400,7 +41400,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="n">
@@ -41495,7 +41495,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="n">
@@ -41590,7 +41590,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="n">
@@ -41685,7 +41685,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="n">
@@ -41780,7 +41780,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="inlineStr"/>
@@ -41873,7 +41873,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="inlineStr"/>
@@ -41966,7 +41966,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="inlineStr"/>
@@ -42059,7 +42059,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="inlineStr"/>
@@ -42152,7 +42152,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="inlineStr"/>
@@ -42245,7 +42245,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="inlineStr"/>
@@ -42338,7 +42338,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="inlineStr"/>
@@ -42431,7 +42431,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="inlineStr"/>
@@ -42524,7 +42524,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="inlineStr"/>
@@ -42617,7 +42617,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="inlineStr"/>
@@ -42710,7 +42710,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="inlineStr"/>
@@ -42803,7 +42803,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="inlineStr"/>
@@ -42896,7 +42896,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="inlineStr"/>
@@ -42989,7 +42989,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="inlineStr"/>
@@ -43082,7 +43082,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="inlineStr"/>
@@ -43175,7 +43175,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="inlineStr"/>
@@ -43268,7 +43268,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="inlineStr"/>
@@ -43361,7 +43361,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="inlineStr"/>
@@ -43454,7 +43454,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="inlineStr"/>
@@ -43547,7 +43547,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="inlineStr"/>
@@ -43640,7 +43640,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="inlineStr"/>
@@ -43733,7 +43733,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="inlineStr"/>
@@ -43826,7 +43826,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="inlineStr"/>
@@ -43919,7 +43919,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="inlineStr"/>
@@ -44012,7 +44012,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="inlineStr"/>
@@ -44105,7 +44105,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="inlineStr"/>
@@ -44198,7 +44198,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="inlineStr"/>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="inlineStr"/>
@@ -44384,7 +44384,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="inlineStr"/>
@@ -44477,7 +44477,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="inlineStr"/>
@@ -44570,7 +44570,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="inlineStr"/>
@@ -44663,7 +44663,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="inlineStr"/>
@@ -44756,7 +44756,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>26-03-2021 08:30</t>
+          <t>2021-03-26 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="inlineStr"/>
@@ -44849,7 +44849,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="inlineStr"/>
@@ -44942,7 +44942,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="inlineStr"/>
@@ -45035,7 +45035,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="inlineStr"/>
@@ -45128,7 +45128,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="n">
@@ -45223,7 +45223,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="n">
@@ -45318,7 +45318,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="n">
@@ -45413,7 +45413,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="n">
@@ -45508,7 +45508,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="n">
@@ -45603,7 +45603,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="n">
@@ -45698,7 +45698,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="n">
@@ -45793,7 +45793,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>24-09-2021 08:30</t>
+          <t>2021-09-24 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="n">
@@ -45888,7 +45888,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="n">
@@ -45983,7 +45983,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>06-11-2021 08:30</t>
+          <t>2021-06-11 08:30:00</t>
         </is>
       </c>
       <c r="T481" t="n">
@@ -46078,7 +46078,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T482" t="n">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T483" t="n">
@@ -46274,7 +46274,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T484" t="n">
@@ -46375,7 +46375,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>02-10-2021 08:30</t>
+          <t>2021-02-10 08:30:00</t>
         </is>
       </c>
       <c r="T485" t="n">
@@ -46476,7 +46476,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T486" t="n">
@@ -46577,7 +46577,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T487" t="n">
@@ -46678,7 +46678,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T488" t="n">
@@ -46773,7 +46773,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T489" t="n">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T490" t="n">
@@ -46963,7 +46963,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T491" t="n">
@@ -47058,7 +47058,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T492" t="n">
@@ -47153,7 +47153,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T493" t="n">
@@ -47248,7 +47248,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T494" t="n">
@@ -47343,7 +47343,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>24-09-2021 08:30</t>
+          <t>2021-09-24 08:30:00</t>
         </is>
       </c>
       <c r="T495" t="n">
@@ -47438,7 +47438,7 @@
       </c>
       <c r="S496" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T496" t="n">
@@ -47533,7 +47533,7 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>06-11-2021 08:30</t>
+          <t>2021-06-11 08:30:00</t>
         </is>
       </c>
       <c r="T497" t="n">
@@ -47628,7 +47628,7 @@
       </c>
       <c r="S498" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T498" t="n">
@@ -47723,7 +47723,7 @@
       </c>
       <c r="S499" t="inlineStr">
         <is>
-          <t>02-04-2021 08:30</t>
+          <t>2021-02-04 08:30:00</t>
         </is>
       </c>
       <c r="T499" t="n">
@@ -47824,7 +47824,7 @@
       </c>
       <c r="S500" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T500" t="n">
@@ -47925,7 +47925,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T501" t="inlineStr"/>
@@ -48018,7 +48018,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T502" t="inlineStr"/>
@@ -48111,7 +48111,7 @@
       </c>
       <c r="S503" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T503" t="inlineStr"/>
@@ -48204,7 +48204,7 @@
       </c>
       <c r="S504" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T504" t="inlineStr"/>
@@ -48297,7 +48297,7 @@
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T505" t="inlineStr"/>
@@ -48390,7 +48390,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T506" t="inlineStr"/>
@@ -48483,7 +48483,7 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T507" t="inlineStr"/>
@@ -48576,7 +48576,7 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T508" t="inlineStr"/>
@@ -48669,7 +48669,7 @@
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T509" t="inlineStr"/>
@@ -48762,7 +48762,7 @@
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T510" t="inlineStr"/>
@@ -48855,7 +48855,7 @@
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T511" t="inlineStr"/>
@@ -48948,7 +48948,7 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T512" t="n">
@@ -49049,7 +49049,7 @@
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T513" t="n">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T514" t="n">
